--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DFS_HRM-2031-0352/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DFS_HRM-2031-0352/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.40945</v>
+        <v>16.58371</v>
       </c>
       <c r="D2" t="n">
-        <v>16.72872</v>
+        <v>16.3971</v>
       </c>
       <c r="E2" t="n">
-        <v>16.80513</v>
+        <v>16.4785</v>
       </c>
       <c r="F2" t="n">
-        <v>42.13832</v>
+        <v>41.97976</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05021</v>
+        <v>0.05047</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81455</v>
+        <v>1.82038</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.63209</v>
+        <v>16.38182</v>
       </c>
       <c r="D3" t="n">
-        <v>16.20636</v>
+        <v>16.34276</v>
       </c>
       <c r="E3" t="n">
-        <v>16.6005</v>
+        <v>16.35849</v>
       </c>
       <c r="F3" t="n">
-        <v>42.20369</v>
+        <v>42.53852</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05017</v>
+        <v>0.0495</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81808</v>
+        <v>1.78331</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.53754</v>
+        <v>16.88848</v>
       </c>
       <c r="D4" t="n">
-        <v>16.27724</v>
+        <v>16.70454</v>
       </c>
       <c r="E4" t="n">
-        <v>16.60848</v>
+        <v>16.74844</v>
       </c>
       <c r="F4" t="n">
-        <v>41.67598</v>
+        <v>41.73634</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05009</v>
+        <v>0.05048</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81281</v>
+        <v>1.84151</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.87452</v>
+        <v>16.80373</v>
       </c>
       <c r="D6" t="n">
-        <v>16.22128</v>
+        <v>15.70873</v>
       </c>
       <c r="E6" t="n">
-        <v>16.06894</v>
+        <v>16.34822</v>
       </c>
       <c r="F6" t="n">
-        <v>21.9525</v>
+        <v>21.85911</v>
       </c>
       <c r="G6" t="n">
-        <v>34.12159</v>
+        <v>34.02274</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.46081</v>
+        <v>16.96131</v>
       </c>
       <c r="D7" t="n">
-        <v>15.96467</v>
+        <v>15.59801</v>
       </c>
       <c r="E7" t="n">
-        <v>16.7042</v>
+        <v>16.15458</v>
       </c>
       <c r="F7" t="n">
-        <v>21.64353</v>
+        <v>21.72274</v>
       </c>
       <c r="G7" t="n">
-        <v>34.56616</v>
+        <v>33.88502</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.07257</v>
+        <v>16.61497</v>
       </c>
       <c r="D8" t="n">
-        <v>16.07773</v>
+        <v>15.7369</v>
       </c>
       <c r="E8" t="n">
-        <v>16.2274</v>
+        <v>16.14595</v>
       </c>
       <c r="F8" t="n">
-        <v>21.49328</v>
+        <v>21.78517</v>
       </c>
       <c r="G8" t="n">
-        <v>34.14277</v>
+        <v>33.69702</v>
       </c>
     </row>
   </sheetData>
